--- a/internal_doc/05.测试设计/场景细分表.xlsx
+++ b/internal_doc/05.测试设计/场景细分表.xlsx
@@ -17,7 +17,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="149">
+  <si>
+    <t>网络单通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>节点正常重启</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -172,15 +176,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>createCL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>range切分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲突切分</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -375,10 +371,6 @@
   <si>
     <t xml:space="preserve">关注cs、cl个数限制，domain个数限制等
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>切分最大任务数、切分边界、全部切分过去</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -649,6 +641,40 @@
   </si>
   <si>
     <t>关注切分任务能否继续进行；数据是否正确切分；组内数据是否一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分最大任务数、切分边界、全部切分过去、边界冲突</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不影响切分任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不影响切分任务</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同range切分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、rang切分时源主节点正常重启；切主后继续执行切分，且切分正确
+2、range切分时，目的主节点正常重启；其余节点继续执行切分，必得故障后任务不会冲突，且切分正确</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建CS时，catalog主节点断网，恢复后catalog数据是否一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、创建CL时，catalog主节点断网
+2、创建CL时，指定group下的数据主节点断网</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -866,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -969,6 +995,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:T67"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="12.125" style="4" customWidth="1"/>
@@ -1352,73 +1390,77 @@
     <col min="16" max="16" width="19.375" style="4" customWidth="1"/>
     <col min="17" max="17" width="11.375" style="4" customWidth="1"/>
     <col min="18" max="18" width="17.25" style="41" customWidth="1"/>
-    <col min="19" max="19" width="17.625" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="4"/>
+    <col min="19" max="19" width="8" style="41" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.625" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="36">
+    <row r="1" spans="1:20" ht="36">
       <c r="A1" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="23" t="s">
-        <v>92</v>
-      </c>
       <c r="L1" s="23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="S1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="24">
+      <c r="T1" s="33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="24">
       <c r="A2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -1435,73 +1477,75 @@
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" s="35"/>
-      <c r="S2" s="34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="132">
+      <c r="S2" s="43"/>
+      <c r="T2" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="132">
       <c r="A3" s="8"/>
       <c r="B3" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="F3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="H3" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="Q3" s="26"/>
       <c r="R3" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="S3" s="34"/>
-    </row>
-    <row r="4" spans="1:19">
+        <v>96</v>
+      </c>
+      <c r="S3" s="43"/>
+      <c r="T3" s="34"/>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -1518,15 +1562,16 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="26"/>
       <c r="R4" s="36"/>
-      <c r="S4" s="34"/>
-    </row>
-    <row r="5" spans="1:19" ht="24">
+      <c r="S4" s="44"/>
+      <c r="T4" s="34"/>
+    </row>
+    <row r="5" spans="1:20" ht="24">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1543,62 +1588,64 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="26"/>
       <c r="R5" s="36"/>
-      <c r="S5" s="34"/>
-    </row>
-    <row r="6" spans="1:19" ht="36">
+      <c r="S5" s="44"/>
+      <c r="T5" s="34"/>
+    </row>
+    <row r="6" spans="1:20" ht="36">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="L6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="N6" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q6" s="26"/>
       <c r="R6" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="S6" s="34"/>
-    </row>
-    <row r="7" spans="1:19">
+        <v>96</v>
+      </c>
+      <c r="S6" s="43"/>
+      <c r="T6" s="34"/>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="8"/>
       <c r="B7" s="2"/>
       <c r="C7" s="7"/>
@@ -1617,9 +1664,10 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="26"/>
       <c r="R7" s="36"/>
-      <c r="S7" s="34"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="S7" s="44"/>
+      <c r="T7" s="34"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="10"/>
       <c r="B8" s="9"/>
       <c r="C8" s="7"/>
@@ -1638,74 +1686,76 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="27"/>
       <c r="R8" s="36"/>
-      <c r="S8" s="34"/>
-    </row>
-    <row r="9" spans="1:19" ht="96">
+      <c r="S8" s="44"/>
+      <c r="T8" s="34"/>
+    </row>
+    <row r="9" spans="1:20" ht="96">
       <c r="A9" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>121</v>
-      </c>
       <c r="J9" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K9" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="M9" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>84</v>
-      </c>
       <c r="R9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="S9" s="38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>96</v>
+      </c>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="13"/>
       <c r="B10" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
@@ -1722,15 +1772,16 @@
       <c r="P10" s="17"/>
       <c r="Q10" s="29"/>
       <c r="R10" s="37"/>
-      <c r="S10" s="38"/>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="S10" s="45"/>
+      <c r="T10" s="38"/>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="13"/>
       <c r="B11" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
@@ -1747,68 +1798,70 @@
       <c r="P11" s="17"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="37"/>
-      <c r="S11" s="38"/>
-    </row>
-    <row r="12" spans="1:19" ht="84">
+      <c r="S11" s="45"/>
+      <c r="T11" s="38"/>
+    </row>
+    <row r="12" spans="1:20" ht="84">
       <c r="A12" s="13"/>
       <c r="B12" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="G12" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="K12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="J12" s="17" t="s">
+      <c r="N12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="P12" s="17" t="s">
         <v>126</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="P12" s="17" t="s">
-        <v>128</v>
       </c>
       <c r="Q12" s="29"/>
       <c r="R12" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S12" s="38"/>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" s="38"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="13"/>
       <c r="B13" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
@@ -1825,15 +1878,16 @@
       <c r="P13" s="17"/>
       <c r="Q13" s="29"/>
       <c r="R13" s="37"/>
-      <c r="S13" s="38"/>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="S13" s="45"/>
+      <c r="T13" s="38"/>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="13"/>
       <c r="B14" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1850,15 +1904,16 @@
       <c r="P14" s="17"/>
       <c r="Q14" s="29"/>
       <c r="R14" s="37"/>
-      <c r="S14" s="38"/>
-    </row>
-    <row r="15" spans="1:19" ht="24">
+      <c r="S14" s="45"/>
+      <c r="T14" s="38"/>
+    </row>
+    <row r="15" spans="1:20" ht="24">
       <c r="A15" s="13"/>
       <c r="B15" s="12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
@@ -1875,15 +1930,16 @@
       <c r="P15" s="17"/>
       <c r="Q15" s="29"/>
       <c r="R15" s="37"/>
-      <c r="S15" s="38"/>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="S15" s="45"/>
+      <c r="T15" s="38"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="13"/>
       <c r="B16" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -1900,15 +1956,16 @@
       <c r="P16" s="17"/>
       <c r="Q16" s="29"/>
       <c r="R16" s="37"/>
-      <c r="S16" s="38"/>
-    </row>
-    <row r="17" spans="1:19" ht="24">
+      <c r="S16" s="45"/>
+      <c r="T16" s="38"/>
+    </row>
+    <row r="17" spans="1:20" ht="24">
       <c r="A17" s="13"/>
       <c r="B17" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -1925,15 +1982,16 @@
       <c r="P17" s="17"/>
       <c r="Q17" s="29"/>
       <c r="R17" s="37"/>
-      <c r="S17" s="38"/>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="S17" s="45"/>
+      <c r="T17" s="38"/>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" s="13"/>
       <c r="B18" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
@@ -1950,68 +2008,70 @@
       <c r="P18" s="17"/>
       <c r="Q18" s="29"/>
       <c r="R18" s="37"/>
-      <c r="S18" s="38"/>
-    </row>
-    <row r="19" spans="1:19" ht="60">
+      <c r="S18" s="45"/>
+      <c r="T18" s="38"/>
+    </row>
+    <row r="19" spans="1:20" ht="60">
       <c r="A19" s="13"/>
       <c r="B19" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="M19" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>140</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q19" s="29"/>
       <c r="R19" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S19" s="38"/>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19" s="38"/>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="13"/>
       <c r="B20" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -2028,15 +2088,16 @@
       <c r="P20" s="17"/>
       <c r="Q20" s="29"/>
       <c r="R20" s="37"/>
-      <c r="S20" s="38"/>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="S20" s="45"/>
+      <c r="T20" s="38"/>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="13"/>
       <c r="B21" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
@@ -2053,9 +2114,10 @@
       <c r="P21" s="17"/>
       <c r="Q21" s="29"/>
       <c r="R21" s="37"/>
-      <c r="S21" s="38"/>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="S21" s="45"/>
+      <c r="T21" s="38"/>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="13"/>
       <c r="B22" s="12"/>
       <c r="C22" s="17"/>
@@ -2074,12 +2136,13 @@
       <c r="P22" s="17"/>
       <c r="Q22" s="29"/>
       <c r="R22" s="37"/>
-      <c r="S22" s="38"/>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="S22" s="45"/>
+      <c r="T22" s="38"/>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -2097,12 +2160,13 @@
       <c r="P23" s="17"/>
       <c r="Q23" s="29"/>
       <c r="R23" s="37"/>
-      <c r="S23" s="38"/>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="S23" s="45"/>
+      <c r="T23" s="38"/>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -2120,9 +2184,10 @@
       <c r="P24" s="17"/>
       <c r="Q24" s="29"/>
       <c r="R24" s="37"/>
-      <c r="S24" s="38"/>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="S24" s="45"/>
+      <c r="T24" s="38"/>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="15"/>
       <c r="B25" s="12"/>
       <c r="C25" s="17"/>
@@ -2141,16 +2206,19 @@
       <c r="P25" s="17"/>
       <c r="Q25" s="30"/>
       <c r="R25" s="37"/>
-      <c r="S25" s="38"/>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="S25" s="45"/>
+      <c r="T25" s="38"/>
+    </row>
+    <row r="26" spans="1:20" ht="36">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -2165,19 +2233,22 @@
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R26" s="35"/>
-      <c r="S26" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="S26" s="43"/>
+      <c r="T26" s="40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="48">
       <c r="A27" s="8"/>
       <c r="B27" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="9"/>
+        <v>147</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>148</v>
+      </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -2193,12 +2264,13 @@
       <c r="P27" s="9"/>
       <c r="Q27" s="31"/>
       <c r="R27" s="35"/>
-      <c r="S27" s="40"/>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="S27" s="43"/>
+      <c r="T27" s="40"/>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="8"/>
       <c r="B28" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2216,12 +2288,13 @@
       <c r="P28" s="9"/>
       <c r="Q28" s="31"/>
       <c r="R28" s="35"/>
-      <c r="S28" s="40"/>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="S28" s="43"/>
+      <c r="T28" s="40"/>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="8"/>
       <c r="B29" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2239,12 +2312,13 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="31"/>
       <c r="R29" s="35"/>
-      <c r="S29" s="40"/>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="S29" s="43"/>
+      <c r="T29" s="40"/>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" s="8"/>
       <c r="B30" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -2262,12 +2336,13 @@
       <c r="P30" s="9"/>
       <c r="Q30" s="31"/>
       <c r="R30" s="35"/>
-      <c r="S30" s="40"/>
-    </row>
-    <row r="31" spans="1:19" ht="24">
+      <c r="S30" s="43"/>
+      <c r="T30" s="40"/>
+    </row>
+    <row r="31" spans="1:20" ht="24">
       <c r="A31" s="8"/>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -2285,12 +2360,13 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="31"/>
       <c r="R31" s="35"/>
-      <c r="S31" s="40"/>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="S31" s="43"/>
+      <c r="T31" s="40"/>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="8"/>
       <c r="B32" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -2308,9 +2384,10 @@
       <c r="P32" s="9"/>
       <c r="Q32" s="31"/>
       <c r="R32" s="35"/>
-      <c r="S32" s="40"/>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="S32" s="43"/>
+      <c r="T32" s="40"/>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" s="10"/>
       <c r="B33" s="16"/>
       <c r="C33" s="9"/>
@@ -2329,63 +2406,69 @@
       <c r="P33" s="9"/>
       <c r="Q33" s="32"/>
       <c r="R33" s="35"/>
-      <c r="S33" s="40"/>
-    </row>
-    <row r="34" spans="1:19" ht="84">
+      <c r="S33" s="43"/>
+      <c r="T33" s="40"/>
+    </row>
+    <row r="34" spans="1:20" ht="108">
       <c r="A34" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>142</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>142</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="M34" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="M34" s="17" t="s">
+        <v>145</v>
+      </c>
       <c r="N34" s="17"/>
       <c r="O34" s="17"/>
       <c r="P34" s="17"/>
       <c r="Q34" s="28" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="R34" s="37"/>
-      <c r="S34" s="38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="S34" s="45"/>
+      <c r="T34" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" s="13"/>
       <c r="B35" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="17"/>
+        <v>14</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
@@ -2401,13 +2484,12 @@
       <c r="P35" s="17"/>
       <c r="Q35" s="29"/>
       <c r="R35" s="37"/>
-      <c r="S35" s="38"/>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="S35" s="45"/>
+      <c r="T35" s="38"/>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" s="13"/>
-      <c r="B36" s="12" t="s">
-        <v>40</v>
-      </c>
+      <c r="B36" s="12"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -2424,12 +2506,13 @@
       <c r="P36" s="17"/>
       <c r="Q36" s="29"/>
       <c r="R36" s="37"/>
-      <c r="S36" s="38"/>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="S36" s="45"/>
+      <c r="T36" s="38"/>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37" s="13"/>
       <c r="B37" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -2447,9 +2530,10 @@
       <c r="P37" s="17"/>
       <c r="Q37" s="29"/>
       <c r="R37" s="37"/>
-      <c r="S37" s="38"/>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="S37" s="45"/>
+      <c r="T37" s="38"/>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38" s="13"/>
       <c r="B38" s="12"/>
       <c r="C38" s="17"/>
@@ -2468,9 +2552,10 @@
       <c r="P38" s="17"/>
       <c r="Q38" s="29"/>
       <c r="R38" s="37"/>
-      <c r="S38" s="38"/>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="S38" s="45"/>
+      <c r="T38" s="38"/>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" s="15"/>
       <c r="B39" s="12"/>
       <c r="C39" s="17"/>
@@ -2489,14 +2574,15 @@
       <c r="P39" s="17"/>
       <c r="Q39" s="30"/>
       <c r="R39" s="37"/>
-      <c r="S39" s="38"/>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="S39" s="45"/>
+      <c r="T39" s="38"/>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>41</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -2513,17 +2599,18 @@
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R40" s="35"/>
-      <c r="S40" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="S40" s="43"/>
+      <c r="T40" s="40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" s="8"/>
       <c r="B41" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -2541,12 +2628,13 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="31"/>
       <c r="R41" s="35"/>
-      <c r="S41" s="40"/>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="S41" s="43"/>
+      <c r="T41" s="40"/>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" s="8"/>
       <c r="B42" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -2564,9 +2652,10 @@
       <c r="P42" s="9"/>
       <c r="Q42" s="31"/>
       <c r="R42" s="35"/>
-      <c r="S42" s="40"/>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="S42" s="43"/>
+      <c r="T42" s="40"/>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" s="8"/>
       <c r="B43" s="16"/>
       <c r="C43" s="9"/>
@@ -2585,9 +2674,10 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="31"/>
       <c r="R43" s="35"/>
-      <c r="S43" s="40"/>
-    </row>
-    <row r="44" spans="1:19">
+      <c r="S43" s="43"/>
+      <c r="T43" s="40"/>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" s="10"/>
       <c r="B44" s="16"/>
       <c r="C44" s="9"/>
@@ -2606,14 +2696,15 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="32"/>
       <c r="R44" s="35"/>
-      <c r="S44" s="40"/>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="S44" s="43"/>
+      <c r="T44" s="40"/>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -2630,17 +2721,18 @@
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
       <c r="Q45" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R45" s="37"/>
-      <c r="S45" s="38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="S45" s="45"/>
+      <c r="T45" s="38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46" s="13"/>
       <c r="B46" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
@@ -2658,12 +2750,13 @@
       <c r="P46" s="17"/>
       <c r="Q46" s="29"/>
       <c r="R46" s="37"/>
-      <c r="S46" s="38"/>
-    </row>
-    <row r="47" spans="1:19">
+      <c r="S46" s="45"/>
+      <c r="T46" s="38"/>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47" s="13"/>
       <c r="B47" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -2681,12 +2774,13 @@
       <c r="P47" s="17"/>
       <c r="Q47" s="29"/>
       <c r="R47" s="37"/>
-      <c r="S47" s="38"/>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="S47" s="45"/>
+      <c r="T47" s="38"/>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48" s="13"/>
       <c r="B48" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -2704,12 +2798,13 @@
       <c r="P48" s="17"/>
       <c r="Q48" s="29"/>
       <c r="R48" s="37"/>
-      <c r="S48" s="38"/>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="S48" s="45"/>
+      <c r="T48" s="38"/>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49" s="13"/>
       <c r="B49" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -2727,12 +2822,13 @@
       <c r="P49" s="17"/>
       <c r="Q49" s="29"/>
       <c r="R49" s="37"/>
-      <c r="S49" s="38"/>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="S49" s="45"/>
+      <c r="T49" s="38"/>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50" s="13"/>
       <c r="B50" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -2750,12 +2846,13 @@
       <c r="P50" s="17"/>
       <c r="Q50" s="29"/>
       <c r="R50" s="37"/>
-      <c r="S50" s="38"/>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="S50" s="45"/>
+      <c r="T50" s="38"/>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51" s="13"/>
       <c r="B51" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -2773,12 +2870,13 @@
       <c r="P51" s="17"/>
       <c r="Q51" s="29"/>
       <c r="R51" s="37"/>
-      <c r="S51" s="38"/>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="S51" s="45"/>
+      <c r="T51" s="38"/>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52" s="13"/>
       <c r="B52" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -2796,12 +2894,13 @@
       <c r="P52" s="17"/>
       <c r="Q52" s="29"/>
       <c r="R52" s="37"/>
-      <c r="S52" s="38"/>
-    </row>
-    <row r="53" spans="1:19">
+      <c r="S52" s="45"/>
+      <c r="T52" s="38"/>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53" s="13"/>
       <c r="B53" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -2819,12 +2918,13 @@
       <c r="P53" s="17"/>
       <c r="Q53" s="29"/>
       <c r="R53" s="37"/>
-      <c r="S53" s="38"/>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="S53" s="45"/>
+      <c r="T53" s="38"/>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54" s="13"/>
       <c r="B54" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -2842,12 +2942,13 @@
       <c r="P54" s="17"/>
       <c r="Q54" s="29"/>
       <c r="R54" s="37"/>
-      <c r="S54" s="38"/>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="S54" s="45"/>
+      <c r="T54" s="38"/>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55" s="13"/>
       <c r="B55" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -2865,12 +2966,13 @@
       <c r="P55" s="17"/>
       <c r="Q55" s="29"/>
       <c r="R55" s="37"/>
-      <c r="S55" s="38"/>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="S55" s="45"/>
+      <c r="T55" s="38"/>
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56" s="13"/>
       <c r="B56" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -2888,12 +2990,13 @@
       <c r="P56" s="17"/>
       <c r="Q56" s="29"/>
       <c r="R56" s="37"/>
-      <c r="S56" s="38"/>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="S56" s="45"/>
+      <c r="T56" s="38"/>
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57" s="13"/>
       <c r="B57" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -2911,12 +3014,13 @@
       <c r="P57" s="17"/>
       <c r="Q57" s="29"/>
       <c r="R57" s="37"/>
-      <c r="S57" s="38"/>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="S57" s="45"/>
+      <c r="T57" s="38"/>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58" s="13"/>
       <c r="B58" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -2934,12 +3038,13 @@
       <c r="P58" s="17"/>
       <c r="Q58" s="29"/>
       <c r="R58" s="37"/>
-      <c r="S58" s="38"/>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="S58" s="45"/>
+      <c r="T58" s="38"/>
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59" s="13"/>
       <c r="B59" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -2957,9 +3062,10 @@
       <c r="P59" s="17"/>
       <c r="Q59" s="29"/>
       <c r="R59" s="37"/>
-      <c r="S59" s="38"/>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="S59" s="45"/>
+      <c r="T59" s="38"/>
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60" s="15"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -2978,14 +3084,15 @@
       <c r="P60" s="17"/>
       <c r="Q60" s="30"/>
       <c r="R60" s="37"/>
-      <c r="S60" s="38"/>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="S60" s="45"/>
+      <c r="T60" s="38"/>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
@@ -3002,17 +3109,18 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R61" s="35"/>
-      <c r="S61" s="40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="24">
+      <c r="S61" s="43"/>
+      <c r="T61" s="40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="24">
       <c r="A62" s="19"/>
       <c r="B62" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
@@ -3030,12 +3138,13 @@
       <c r="P62" s="9"/>
       <c r="Q62" s="31"/>
       <c r="R62" s="35"/>
-      <c r="S62" s="40"/>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="S62" s="43"/>
+      <c r="T62" s="40"/>
+    </row>
+    <row r="63" spans="1:20">
       <c r="A63" s="19"/>
       <c r="B63" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
@@ -3053,9 +3162,10 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="31"/>
       <c r="R63" s="35"/>
-      <c r="S63" s="40"/>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="S63" s="43"/>
+      <c r="T63" s="40"/>
+    </row>
+    <row r="64" spans="1:20">
       <c r="A64" s="19"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -3074,9 +3184,10 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="31"/>
       <c r="R64" s="35"/>
-      <c r="S64" s="40"/>
-    </row>
-    <row r="65" spans="1:19">
+      <c r="S64" s="43"/>
+      <c r="T64" s="40"/>
+    </row>
+    <row r="65" spans="1:20">
       <c r="A65" s="19"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -3095,9 +3206,10 @@
       <c r="P65" s="9"/>
       <c r="Q65" s="31"/>
       <c r="R65" s="35"/>
-      <c r="S65" s="40"/>
-    </row>
-    <row r="66" spans="1:19">
+      <c r="S65" s="43"/>
+      <c r="T65" s="40"/>
+    </row>
+    <row r="66" spans="1:20">
       <c r="A66" s="19"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -3116,9 +3228,10 @@
       <c r="P66" s="9"/>
       <c r="Q66" s="31"/>
       <c r="R66" s="35"/>
-      <c r="S66" s="40"/>
-    </row>
-    <row r="67" spans="1:19">
+      <c r="S66" s="43"/>
+      <c r="T66" s="40"/>
+    </row>
+    <row r="67" spans="1:20">
       <c r="A67" s="20"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -3137,7 +3250,8 @@
       <c r="P67" s="9"/>
       <c r="Q67" s="32"/>
       <c r="R67" s="35"/>
-      <c r="S67" s="40"/>
+      <c r="S67" s="43"/>
+      <c r="T67" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3174,31 +3288,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="5"/>
     </row>
@@ -3236,12 +3350,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/场景细分表.xlsx
+++ b/internal_doc/05.测试设计/场景细分表.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="160">
   <si>
     <t>节点正常重启</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -44,10 +44,6 @@
   </si>
   <si>
     <t>createCS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -268,12 +264,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、源节点断网后，切换源节点进行数据同步
-2、源节点断网恢复，不影响现有的恢复流程
-3、目的节点断网恢复后，继续同步数据，数据一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、源节点闪断，不影响数据同步流程
 2、目的节点闪断，不影响数据同步流程</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -333,12 +323,6 @@
   <si>
     <t>1、源节点磁盘满，不影响同步流程（待分析）
 2、目的节点磁盘恢复后，继续做数据同步</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、源节点所在主机异常重启，在副本足够的情况下目的节点选择其它节点进行同步
-2、副本不足时，目的节点等待源节点rebuild完毕后继续同步（源节点会有数据丢失）
-3、目的节点所在主机重启后，继续做同步</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -525,27 +509,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>创建CS时，catalog主节点断网，恢复后catalog数据是否一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>createCL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、创建CL时，catalog主节点断网
 2、创建CL时，指定group下的数据主节点断网</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、insert操作时，主节点断网；恢复后数据不丢失/数据极少量丢失
-2、insert操作时，备节点断网；数据不丢失
-3、insert操作时，所有节点断网恢复后；数据不丢失/数据极少量丢失</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、主节点异常重启，操作失败，重新选主后恢复正常。（会丢数据）
-2、备节点异常重启，不影响操作（注意relpsize）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -596,36 +565,6 @@
   </si>
   <si>
     <t>2、attach时，catalog主节点断网；恢复后catalog元数据须一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、源节点异常重启，在副本足够的情况下目的节点选择其它节点进行同步
-2、副本不足时，目的节点等待源节点rebuild完毕后继续同步</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（源节点会有数据丢失）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3、目的节点重启后，继续做同步</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -847,6 +786,107 @@
   </si>
   <si>
     <t>网络单通（低优先级）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、主节点异常重启，操作失败，重新选主后恢复正常。（会丢数据）
+2、备节点异常重启，不影响操作（注意relpsize）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、insert操作时，主节点断网；恢复后数据不丢失/数据极少量丢失
+2、insert操作时，备节点断网；数据不丢失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、源节点断网后，切换源节点进行数据同步
+2、旧的源节点断网恢复，不影响现有的恢复流程
+3、目的节点断网恢复后，继续同步数据，数据一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、源节点异常重启，在副本足够的情况下目的节点选择其它节点进行同步
+2、副本不足时，目的节点等待源节点rebuild完毕后继续同步</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（源节点会有数据丢失）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3、目的节点重启后，继续做同步，数据不丢失且一致</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、源节点所在主机异常重启，在副本足够的情况下目的节点选择其它节点进行同步
+2、副本不足时，目的节点等待源节点rebuild完毕后继续同步（源节点会有数据丢失）
+3、目的节点所在主机重启后，继续做同步，数据不丢失且一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、创建CS时，catalog主节点断网，恢复后catalog数据是否一致
+2、创建CS时，catalog备节点断网，恢复后数据是否一致</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别对主备catalog进行故障，应不影响数据一致性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别对主备catalog进行故障，恢复后应不影响数据一致性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高并发创建CS，关注功能是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别对主备catalog进行故障，恢复后应不影响数据一致性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该退出进程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该退出进程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要关注节点能否报错、是否能够恢复及数据不丢失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要关注节点能否报错、是否能够恢复及数据不丢失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cerateCL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1052,31 +1092,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1116,8 +1134,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1128,14 +1152,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1499,62 +1541,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T67"/>
+  <dimension ref="A1:T65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="12.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="6.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.375" style="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="4" customWidth="1"/>
     <col min="5" max="6" width="13.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.75" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.875" style="4" customWidth="1"/>
     <col min="10" max="10" width="11.25" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14.125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="16.5" style="4" customWidth="1"/>
-    <col min="15" max="15" width="15.125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="13.375" style="28" customWidth="1"/>
+    <col min="12" max="12" width="15.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="19.75" style="4" customWidth="1"/>
+    <col min="14" max="14" width="22.25" style="4" customWidth="1"/>
+    <col min="15" max="15" width="19.875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="13.375" style="20" customWidth="1"/>
     <col min="17" max="17" width="17.625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="9.5" style="28" customWidth="1"/>
+    <col min="18" max="18" width="9.5" style="20" customWidth="1"/>
     <col min="19" max="19" width="8.125" style="4" customWidth="1"/>
     <col min="20" max="20" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="36">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>0</v>
@@ -1563,36 +1605,36 @@
         <v>1</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="24">
+      <c r="A2" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="S1" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="24">
-      <c r="A2" s="33" t="s">
+      <c r="C2" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>143</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1606,80 +1648,80 @@
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="R2" s="30"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="R2" s="22"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
     </row>
-    <row r="3" spans="1:20" ht="144">
-      <c r="A3" s="15"/>
+    <row r="3" spans="1:20" ht="120">
+      <c r="A3" s="32"/>
       <c r="B3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="32"/>
+      <c r="B4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="N3" s="7" t="s">
+      <c r="C4" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" s="15"/>
-      <c r="B4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -1692,22 +1734,22 @@
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="31"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="23"/>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="1:20" ht="24">
-      <c r="A5" s="15"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>143</v>
+        <v>9</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -1720,72 +1762,72 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="31"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="23"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
     <row r="6" spans="1:20" ht="48">
-      <c r="A6" s="15"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>143</v>
+        <v>34</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="M6" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P6" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="30"/>
+        <v>82</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="22"/>
       <c r="S6" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="15"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="38"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -1798,16 +1840,16 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="31"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="23"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="16"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="38"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -1820,568 +1862,610 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="31"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="23"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:20" ht="132">
-      <c r="A9" s="34" t="s">
-        <v>135</v>
+    <row r="9" spans="1:20" ht="84">
+      <c r="A9" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="17"/>
+      <c r="S9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="37"/>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="37"/>
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="C11" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+    </row>
+    <row r="12" spans="1:20" ht="96">
+      <c r="A12" s="37"/>
+      <c r="B12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q9" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="R9" s="25"/>
-      <c r="S9" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-    </row>
-    <row r="12" spans="1:20" ht="108">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8" t="s">
+      <c r="I12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="37"/>
+      <c r="B13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="T12" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
+      <c r="C13" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="9"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
+      <c r="C14" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:20" ht="36">
-      <c r="A15" s="9"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
+      <c r="C15" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="9"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+    </row>
+    <row r="17" spans="1:20" ht="24">
+      <c r="A17" s="37"/>
+      <c r="B17" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="37"/>
+      <c r="B18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+    </row>
+    <row r="19" spans="1:20" ht="84">
+      <c r="A19" s="37"/>
+      <c r="B19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-    </row>
-    <row r="17" spans="1:20" ht="24">
-      <c r="A17" s="9"/>
-      <c r="B17" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" s="13" t="s">
+      <c r="K19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="37"/>
+      <c r="B20" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="37"/>
+      <c r="B21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="37"/>
+      <c r="B22" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-    </row>
-    <row r="19" spans="1:20" ht="84">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="C22" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="38"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+    </row>
+    <row r="24" spans="1:20" ht="96">
+      <c r="A24" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="T19" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="9"/>
-      <c r="B23" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="11"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-    </row>
-    <row r="26" spans="1:20" ht="48">
-      <c r="A26" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="37" t="s">
-        <v>146</v>
+      <c r="C24" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="P24" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q24" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="R24" s="22"/>
+      <c r="S24" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="T24" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="60">
+      <c r="A25" s="32"/>
+      <c r="B25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="32"/>
+      <c r="B26" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>136</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -2394,25 +2478,21 @@
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="R26" s="30"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="22"/>
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
     </row>
-    <row r="27" spans="1:20" ht="60">
-      <c r="A27" s="15"/>
-      <c r="B27" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>123</v>
-      </c>
+    <row r="27" spans="1:20">
+      <c r="A27" s="32"/>
+      <c r="B27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -2424,19 +2504,19 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="30"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="22"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="15"/>
-      <c r="B28" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>143</v>
+      <c r="A28" s="32"/>
+      <c r="B28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>136</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -2450,19 +2530,19 @@
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="30"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="22"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
     </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="15"/>
-      <c r="B29" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>143</v>
+    <row r="29" spans="1:20" ht="24">
+      <c r="A29" s="32"/>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>136</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -2476,20 +2556,16 @@
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="30"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="22"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="15"/>
-      <c r="B30" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>143</v>
-      </c>
+      <c r="A30" s="32"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="25"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -2502,20 +2578,16 @@
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="30"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="22"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
     </row>
-    <row r="31" spans="1:20" ht="24">
-      <c r="A31" s="15"/>
-      <c r="B31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>143</v>
-      </c>
+    <row r="31" spans="1:20">
+      <c r="A31" s="33"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="25"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -2528,243 +2600,253 @@
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="30"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="22"/>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
     </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="15"/>
-      <c r="B32" s="12" t="s">
+    <row r="32" spans="1:20" ht="120">
+      <c r="A32" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="R32" s="24"/>
+      <c r="S32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="T32" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" s="29"/>
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" s="29"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" s="29"/>
+      <c r="B35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="29"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="30"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+    </row>
+    <row r="38" spans="1:20" ht="60">
+      <c r="A38" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="R38" s="22"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+    </row>
+    <row r="39" spans="1:20" ht="48">
+      <c r="A39" s="32"/>
+      <c r="B39" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="14"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="32"/>
+      <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="16"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-    </row>
-    <row r="34" spans="1:20" ht="120">
-      <c r="A34" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="R34" s="32"/>
-      <c r="S34" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="T34" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="35"/>
-      <c r="B35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="13"/>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="35"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="32"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="13"/>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="35"/>
-      <c r="B37" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="24"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="32"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="13"/>
-    </row>
-    <row r="38" spans="1:20">
-      <c r="A38" s="35"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="13"/>
-      <c r="T38" s="13"/>
-    </row>
-    <row r="39" spans="1:20">
-      <c r="A39" s="36"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="24"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="32"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
-    </row>
-    <row r="40" spans="1:20" ht="60">
-      <c r="A40" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>132</v>
-      </c>
+      <c r="C40" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -2776,25 +2858,17 @@
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="R40" s="30"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="22"/>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
     </row>
-    <row r="41" spans="1:20" ht="48">
-      <c r="A41" s="15"/>
-      <c r="B41" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>133</v>
-      </c>
+    <row r="41" spans="1:20">
+      <c r="A41" s="32"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -2806,20 +2880,16 @@
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
-      <c r="P41" s="22"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="30"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="22"/>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="15"/>
-      <c r="B42" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>147</v>
-      </c>
+      <c r="A42" s="33"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="25"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -2832,481 +2902,491 @@
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="30"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="22"/>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" s="15"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
+      <c r="A43" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="16"/>
+      <c r="Q43" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="R43" s="24"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
     </row>
     <row r="44" spans="1:20">
-      <c r="A44" s="16"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="27"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="24"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="29"/>
+      <c r="B45" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="24"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" s="29"/>
+      <c r="B46" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="24"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" s="29"/>
+      <c r="B47" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="24"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" s="29"/>
+      <c r="B48" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="24"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" s="29"/>
+      <c r="B49" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="24"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" s="29"/>
+      <c r="B50" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="24"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" s="29"/>
+      <c r="B51" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="24"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" s="29"/>
+      <c r="B52" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" s="29"/>
+      <c r="B53" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="24"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" s="29"/>
+      <c r="B54" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="24"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" s="29"/>
+      <c r="B55" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="16"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="24"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" s="29"/>
+      <c r="B56" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="24"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57" s="29"/>
+      <c r="B57" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="24"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58" s="30"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="24"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="14"/>
+      <c r="Q59" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="R59" s="22"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+    </row>
+    <row r="60" spans="1:20" ht="24">
+      <c r="A60" s="32"/>
+      <c r="B60" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="19"/>
+      <c r="R60" s="22"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61" s="32"/>
+      <c r="B61" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>140</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="R45" s="32"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="35"/>
-      <c r="B46" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="25"/>
-      <c r="R46" s="32"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="13"/>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47" s="35"/>
-      <c r="B47" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="25"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="13"/>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48" s="35"/>
-      <c r="B48" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="25"/>
-      <c r="R48" s="32"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="13"/>
-    </row>
-    <row r="49" spans="1:20">
-      <c r="A49" s="35"/>
-      <c r="B49" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="25"/>
-      <c r="R49" s="32"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50" s="35"/>
-      <c r="B50" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="25"/>
-      <c r="R50" s="32"/>
-      <c r="S50" s="13"/>
-      <c r="T50" s="13"/>
-    </row>
-    <row r="51" spans="1:20">
-      <c r="A51" s="35"/>
-      <c r="B51" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="25"/>
-      <c r="R51" s="32"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="13"/>
-    </row>
-    <row r="52" spans="1:20">
-      <c r="A52" s="35"/>
-      <c r="B52" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="25"/>
-      <c r="R52" s="32"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="13"/>
-    </row>
-    <row r="53" spans="1:20">
-      <c r="A53" s="35"/>
-      <c r="B53" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="25"/>
-      <c r="R53" s="32"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="13"/>
-    </row>
-    <row r="54" spans="1:20">
-      <c r="A54" s="35"/>
-      <c r="B54" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="25"/>
-      <c r="R54" s="32"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="13"/>
-    </row>
-    <row r="55" spans="1:20">
-      <c r="A55" s="35"/>
-      <c r="B55" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="32"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="13"/>
-    </row>
-    <row r="56" spans="1:20">
-      <c r="A56" s="35"/>
-      <c r="B56" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C56" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="25"/>
-      <c r="R56" s="32"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="13"/>
-    </row>
-    <row r="57" spans="1:20">
-      <c r="A57" s="35"/>
-      <c r="B57" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C57" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="25"/>
-      <c r="R57" s="32"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="13"/>
-    </row>
-    <row r="58" spans="1:20">
-      <c r="A58" s="35"/>
-      <c r="B58" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="24"/>
-      <c r="Q58" s="25"/>
-      <c r="R58" s="32"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="13"/>
-    </row>
-    <row r="59" spans="1:20">
-      <c r="A59" s="35"/>
-      <c r="B59" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="25"/>
-      <c r="R59" s="32"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="13"/>
-    </row>
-    <row r="60" spans="1:20">
-      <c r="A60" s="36"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="24"/>
-      <c r="Q60" s="25"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="13"/>
-    </row>
-    <row r="61" spans="1:20">
-      <c r="A61" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" s="37" t="s">
-        <v>143</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -3320,22 +3400,16 @@
       <c r="M61" s="7"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="R61" s="30"/>
+      <c r="P61" s="14"/>
+      <c r="Q61" s="19"/>
+      <c r="R61" s="22"/>
       <c r="S61" s="7"/>
       <c r="T61" s="7"/>
     </row>
-    <row r="62" spans="1:20" ht="24">
-      <c r="A62" s="15"/>
-      <c r="B62" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C62" s="37" t="s">
-        <v>143</v>
-      </c>
+    <row r="62" spans="1:20">
+      <c r="A62" s="32"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="25"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
@@ -3348,20 +3422,16 @@
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="27"/>
-      <c r="R62" s="30"/>
+      <c r="P62" s="14"/>
+      <c r="Q62" s="19"/>
+      <c r="R62" s="22"/>
       <c r="S62" s="7"/>
       <c r="T62" s="7"/>
     </row>
     <row r="63" spans="1:20">
-      <c r="A63" s="15"/>
-      <c r="B63" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>147</v>
-      </c>
+      <c r="A63" s="32"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
@@ -3374,16 +3444,16 @@
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="30"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="22"/>
       <c r="S63" s="7"/>
       <c r="T63" s="7"/>
     </row>
     <row r="64" spans="1:20">
-      <c r="A64" s="15"/>
+      <c r="A64" s="32"/>
       <c r="B64" s="7"/>
-      <c r="C64" s="37"/>
+      <c r="C64" s="25"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
@@ -3396,16 +3466,16 @@
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="30"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="22"/>
       <c r="S64" s="7"/>
       <c r="T64" s="7"/>
     </row>
     <row r="65" spans="1:20">
-      <c r="A65" s="15"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="7"/>
-      <c r="C65" s="37"/>
+      <c r="C65" s="25"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -3418,66 +3488,22 @@
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
-      <c r="P65" s="22"/>
-      <c r="Q65" s="27"/>
-      <c r="R65" s="30"/>
+      <c r="P65" s="14"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="22"/>
       <c r="S65" s="7"/>
       <c r="T65" s="7"/>
     </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="15"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="22"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="30"/>
-      <c r="S66" s="7"/>
-      <c r="T66" s="7"/>
-    </row>
-    <row r="67" spans="1:20">
-      <c r="A67" s="16"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-      <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="22"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="7"/>
-      <c r="T67" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A45:A60"/>
-    <mergeCell ref="A61:A67"/>
+    <mergeCell ref="A43:A58"/>
+    <mergeCell ref="A59:A65"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A9:A25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="A9:A23"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A38:A42"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3496,31 +3522,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5"/>
     </row>
@@ -3558,12 +3584,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/场景细分表.xlsx
+++ b/internal_doc/05.测试设计/场景细分表.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="175">
   <si>
     <t>节点正常重启</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -945,9 +945,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>网络拥塞不影响功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>注意事项：
-1、在做故障之前应该先想好如何恢复故障。如用命令模拟断网故障，需要考虑xshell也会断掉。 可以执行后台脚本恢复
-如：cat cutnet.sh
+1、在做故障之前应该先想好如何恢复故障。如用命令模拟断网故障，需要考虑xshell也会断掉。 可以执行后台脚本模拟故障：cat cutnet.sh
 ifdown eth0
 sleep 10
 ifup eth0
@@ -957,7 +960,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>网络拥塞不影响功能</t>
+    <t>不涉及</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1866,7 +1869,7 @@
         <v>76</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>76</v>
@@ -1977,7 +1980,7 @@
         <v>82</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>84</v>
@@ -2912,7 +2915,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>168</v>
@@ -2942,7 +2945,7 @@
         <v>32</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>119</v>
@@ -3714,9 +3717,9 @@
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
     </row>
-    <row r="11" spans="1:2" ht="180">
+    <row r="11" spans="1:2" ht="168">
       <c r="A11" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/internal_doc/05.测试设计/场景细分表.xlsx
+++ b/internal_doc/05.测试设计/场景细分表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="场景细分" sheetId="1" r:id="rId1"/>
@@ -949,18 +949,88 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>注意事项：
-1、在做故障之前应该先想好如何恢复故障。如用命令模拟断网故障，需要考虑xshell也会断掉。 可以执行后台脚本模拟故障：cat cutnet.sh
+    <t>不涉及</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>注意事项：
+1、不明确的需求和预期结果</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>随时跟开发确认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、在做故障之前应该</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>先想好如何恢复故障</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。如用命令模拟断网故障，需要考虑xshell也会断掉。 可以执行后台脚本模拟故障：cat cutnet.sh
 ifdown eth0
 sleep 10
 ifup eth0
 执行时使用后台运行模式
 nohup cutnet.sh &amp; 
-2、测试时，最好顺便把操作记录写到testlink上，方便以后重新测试和问题单回归测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不涉及</t>
+2、写测试用例时，就需要考虑好需要什么工具或脚本。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>等到测试时才考虑
+3、测试时，最好顺便把操作记录写到testlink上，方便以后重新测试和问题单回归测试</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -968,7 +1038,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,6 +1089,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1152,7 +1229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,6 +1338,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1869,7 +1949,7 @@
         <v>76</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>76</v>
@@ -3717,9 +3797,9 @@
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
     </row>
-    <row r="11" spans="1:2" ht="168">
-      <c r="A11" s="13" t="s">
-        <v>173</v>
+    <row r="11" spans="1:2" ht="228">
+      <c r="A11" s="41" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3728,6 +3808,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/internal_doc/05.测试设计/场景细分表.xlsx
+++ b/internal_doc/05.测试设计/场景细分表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="场景细分" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="177">
   <si>
     <t>节点正常重启</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -530,167 +530,6 @@
   </si>
   <si>
     <t>2、attach时，catalog主节点断网；恢复后catalog元数据须一致</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>基本操作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注数据块大小边界、lob块边界;
-关注replSize对数据的影响；
-关注心跳周期；
-是否压缩
-切分后的表
-存在索引的表；）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数据同步</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注同时做同步的最大个数，日志文件个数及大小）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>元数据操作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注cs、cl个数限制，domain个数限制等）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>主子表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注子表最大数量、子表范围边界。插入范围外数据等）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>集群管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注组的个数、节点个数、副本数等）</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>聚集</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（关注大数据量，聚集各种组合）</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -824,6 +663,199 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">1、rang切分时源主节点正常重启；切主后继续执行切分，且切分正确（须考虑单节点）
+2、range切分时，目的主节点正常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、rang切分时源主节点异常重启；切主后继续执行切分，且切分正确（须考虑单节点数据丢失的问题）
+2、range切分时，目的主节点异常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确（备节点为单点时，也不应该丢失数据）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、rang切分时源主节点所在主机异常重启；切主后继续执行切分，且切分正确（须考虑单节点数据丢失的问题）
+2、range切分时，目的主节点所在主机异常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确（备节点为单点时，也不应该丢失数据）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、rang切分时源主节点所在主机正常重启；切主后继续执行切分，且切分正确（须考虑单节点）
+2、range切分时，目的主节点所在主机正常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发多个全量同步/增量同步，多个备节点同时进行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发多个insert不影响操作（并发1000个连接）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大并发query不影响功能（并发1000个连接）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3组3节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3组7节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、创建CL时，catalog主节点断网
+2、创建CL时、catalog备节点断网
+3、创建CL时，指定group下的数据主节点断网
+4、创建CL时，指定group下的数据备节点断网</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景同断网，检查元数据一致，cl成功创建且能做基本操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高并发创建CL，关注功能是否正常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景同断网，检查元数据一致，如果cl成功创建则须确保能做基本操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同createCS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同createCL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、createDomain/dropDomain参考createCS/dropCS
+2、根据domain创建CL的场景可以加入到createCL里面去测</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、detach时，catalog主节点断网；恢复后catalog元数据须一致
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同dropCS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同query</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞不影响功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不涉及</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发支撑？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据同步</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">（关注同时做同步的最大个数，日志文件个数及大小）武赟
+文净、吴艳 </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>基本操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（关注数据块大小边界、lob块边界;
+关注replSize对数据的影响；
+关注心跳周期；
+是否压缩
+切分后的表
+存在索引的表；）友滨
+余婷 吴艳</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>元数据操作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（关注cs、cl个数限制，domain个数限制等）许导
+吴艳、晓妮</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -845,117 +877,97 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>（切分最大任务数、切分边界、全部切分过去、边界冲突、注意单节点的场景）</t>
+      <t>（切分最大任务数、切分边界、全部切分过去、边界冲突、注意单节点的场景）许导
+吴艳 、文净</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、rang切分时源主节点正常重启；切主后继续执行切分，且切分正确（须考虑单节点）
-2、range切分时，目的主节点正常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>主子表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">（关注子表最大数量、子表范围边界。插入范围外数据等）建华
+晓妮、余婷 </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>聚集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">（关注大数据量，聚集各种组合）友滨
+晓妮、余婷 </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>集群管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">（关注组的个数、节点个数、副本数等）钊波
+龙阳、文净
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、rang切分时源主节点异常重启；切主后继续执行切分，且切分正确（须考虑单节点数据丢失的问题）
-2、range切分时，目的主节点异常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确（备节点为单点时，也不应该丢失数据）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、rang切分时源主节点所在主机异常重启；切主后继续执行切分，且切分正确（须考虑单节点数据丢失的问题）
-2、range切分时，目的主节点所在主机异常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确（备节点为单点时，也不应该丢失数据）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、rang切分时源主节点所在主机正常重启；切主后继续执行切分，且切分正确（须考虑单节点）
-2、range切分时，目的主节点所在主机正常重启；备节点升主后继续执行切分，恢复故障后任务不会冲突，且切分正确
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发多个全量同步/增量同步，多个备节点同时进行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发多个insert不影响操作（并发1000个连接）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大并发query不影响功能（并发1000个连接）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3组3节点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3组7节点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、创建CL时，catalog主节点断网
-2、创建CL时、catalog备节点断网
-3、创建CL时，指定group下的数据主节点断网
-4、创建CL时，指定group下的数据备节点断网</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景同断网，检查元数据一致，cl成功创建且能做基本操作</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高并发创建CL，关注功能是否正常</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景同断网，检查元数据一致，如果cl成功创建则须确保能做基本操作</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同createCS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同createCL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、createDomain/dropDomain参考createCS/dropCS
-2、根据domain创建CL的场景可以加入到createCL里面去测</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、detach时，catalog主节点断网；恢复后catalog元数据须一致
-</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同dropCS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>同query</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞不影响功能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不涉及</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <t>注意事项：
-1、不明确的需求和预期结果</t>
+1、有不明确的需求和预期结果</t>
     </r>
     <r>
       <rPr>
@@ -1006,7 +1018,7 @@
 ifup eth0
 执行时使用后台运行模式
 nohup cutnet.sh &amp; 
-2、写测试用例时，就需要考虑好需要什么工具或脚本。</t>
+3、写测试用例时，就需要考虑好需要什么工具或脚本。</t>
     </r>
     <r>
       <rPr>
@@ -1029,8 +1041,12 @@
         <scheme val="minor"/>
       </rPr>
       <t>等到测试时才考虑
-3、测试时，最好顺便把操作记录写到testlink上，方便以后重新测试和问题单回归测试</t>
+4、测试时，最好顺便把操作记录写到testlink上，方便以后重新测试和问题单回归测试</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑部分场景</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1102,7 +1118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1118,6 +1134,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1229,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1342,6 +1364,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1735,7 +1759,7 @@
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="31" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D1" s="31" t="s">
         <v>19</v>
@@ -1780,7 +1804,7 @@
         <v>2</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="S1" s="32" t="s">
         <v>71</v>
@@ -1791,13 +1815,13 @@
     </row>
     <row r="2" spans="1:20" ht="24">
       <c r="A2" s="28" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="18"/>
@@ -1825,10 +1849,10 @@
         <v>58</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>60</v>
@@ -1846,7 +1870,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>72</v>
@@ -1855,10 +1879,10 @@
         <v>86</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="O3" s="17" t="s">
         <v>73</v>
@@ -1883,7 +1907,7 @@
         <v>59</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>75</v>
@@ -1913,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>75</v>
@@ -1943,13 +1967,13 @@
         <v>33</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>76</v>
@@ -2045,22 +2069,22 @@
     </row>
     <row r="9" spans="1:20" ht="84">
       <c r="A9" s="20" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>82</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>84</v>
@@ -2072,7 +2096,7 @@
         <v>81</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="K9" s="19" t="s">
         <v>113</v>
@@ -2081,7 +2105,7 @@
         <v>87</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="N9" s="19" t="s">
         <v>114</v>
@@ -2109,7 +2133,7 @@
         <v>57</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>89</v>
@@ -2139,7 +2163,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>89</v>
@@ -2169,7 +2193,7 @@
         <v>27</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>92</v>
@@ -2190,7 +2214,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K12" s="19" t="s">
         <v>97</v>
@@ -2227,7 +2251,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>89</v>
@@ -2257,7 +2281,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>91</v>
@@ -2287,7 +2311,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>90</v>
@@ -2317,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>102</v>
@@ -2347,7 +2371,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>115</v>
@@ -2377,7 +2401,7 @@
         <v>29</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>91</v>
@@ -2407,7 +2431,7 @@
         <v>54</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>117</v>
@@ -2446,14 +2470,14 @@
         <v>107</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Q19" s="36" t="s">
         <v>101</v>
       </c>
       <c r="R19" s="36"/>
       <c r="S19" s="19" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="T19" s="19" t="s">
         <v>85</v>
@@ -2465,7 +2489,7 @@
         <v>55</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>106</v>
@@ -2495,7 +2519,7 @@
         <v>56</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>106</v>
@@ -2525,7 +2549,7 @@
         <v>93</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -2573,62 +2597,62 @@
     </row>
     <row r="24" spans="1:20" ht="96">
       <c r="A24" s="28" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J24" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="O24" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="M24" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="O24" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="P24" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="Q24" s="38" t="s">
         <v>101</v>
       </c>
       <c r="R24" s="14"/>
       <c r="S24" s="17" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="T24" s="17" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="120">
@@ -2637,43 +2661,43 @@
         <v>112</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O25" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="38" t="s">
@@ -2689,10 +2713,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
@@ -2719,10 +2743,10 @@
         <v>8</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
@@ -2749,10 +2773,10 @@
         <v>9</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
@@ -2779,7 +2803,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -2851,13 +2875,13 @@
     </row>
     <row r="32" spans="1:20" ht="144">
       <c r="A32" s="20" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>118</v>
@@ -2884,19 +2908,19 @@
         <v>108</v>
       </c>
       <c r="L32" s="19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M32" s="19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="N32" s="19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="O32" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="Q32" s="36" t="s">
         <v>101</v>
@@ -2915,7 +2939,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>111</v>
@@ -2989,16 +3013,16 @@
     </row>
     <row r="36" spans="1:20" ht="60">
       <c r="A36" s="28" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
@@ -3025,7 +3049,7 @@
         <v>32</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>119</v>
@@ -3055,7 +3079,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
@@ -3103,16 +3127,16 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="20" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
@@ -3139,10 +3163,10 @@
         <v>38</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
@@ -3169,10 +3193,10 @@
         <v>37</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
@@ -3199,10 +3223,10 @@
         <v>35</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
@@ -3229,10 +3253,10 @@
         <v>36</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
@@ -3259,10 +3283,10 @@
         <v>39</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
@@ -3289,10 +3313,10 @@
         <v>40</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E46" s="19"/>
       <c r="F46" s="19"/>
@@ -3319,10 +3343,10 @@
         <v>41</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
@@ -3349,10 +3373,10 @@
         <v>42</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E48" s="19"/>
       <c r="F48" s="19"/>
@@ -3379,10 +3403,10 @@
         <v>43</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E49" s="19"/>
       <c r="F49" s="19"/>
@@ -3409,10 +3433,10 @@
         <v>44</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E50" s="19"/>
       <c r="F50" s="19"/>
@@ -3439,10 +3463,10 @@
         <v>45</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E51" s="19"/>
       <c r="F51" s="19"/>
@@ -3469,7 +3493,7 @@
         <v>46</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19"/>
@@ -3497,7 +3521,7 @@
         <v>47</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19"/>
@@ -3545,16 +3569,16 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="23" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
@@ -3581,10 +3605,10 @@
         <v>49</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E56" s="17"/>
       <c r="F56" s="17"/>
@@ -3611,10 +3635,10 @@
         <v>68</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
@@ -3754,7 +3778,8 @@
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="30" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="4"/>
+    <col min="2" max="2" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3764,7 +3789,7 @@
       <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="43" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="5"/>
@@ -3776,22 +3801,24 @@
       <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="42" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="5" t="s">
-        <v>158</v>
+      <c r="A5" s="42" t="s">
+        <v>151</v>
       </c>
       <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5"/>
@@ -3799,11 +3826,13 @@
     </row>
     <row r="11" spans="1:2" ht="228">
       <c r="A11" s="41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13" t="s">
+        <v>167</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
